--- a/extenbooks/S1101_extenbook.xlsx
+++ b/extenbooks/S1101_extenbook.xlsx
@@ -21552,7 +21552,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -22907,11 +22907,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22934,76 +22934,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Trade Balances in Major Countries (Fig 11.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1101_research.json", "adequacy_report": "Technical/docs/chapters/CH11_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1101_DPR.md", "epr": "Technical/docs/series/S1101_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1101_load.py", "processor": "Technical/code/P02_processors/P02_S1101_construct.py", "validator": "Technical/code/V03_validators/V03_S1101_validate.py", "processed": "Technical/data/processed/S1101.parquet", "chopped_csv": "Technical/chopped/S1101.csv"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:56:16.880881+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1101_extenbook.xlsx
+++ b/extenbooks/S1101_extenbook.xlsx
@@ -21499,7 +21499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A136"/>
+  <dimension ref="A1:A142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -21894,48 +21894,56 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3. **Within-chapter unit inconsistency with S1104-A.** S1101 uses X/M;</t>
+          <t>3. **Japan (S1101-D) missing year 2000.** The salvaged workbook</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">   S1104-A uses (X-M)/(X+M) per Shaikh's authorial choice in Fig 11.7.</t>
+          <t xml:space="preserve">   (`Appendix11_XMData.xlsx`) skips 2000 for Japan, so S1101-D ships **49 obs**</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (1960-2009 less 2000) rather than 50. This is faithful to the book source —</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t xml:space="preserve">   the gap is preserved verbatim, not interpolated. It is a sourceable</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   completeness gap: the 2000 Japan X/M ratio is recoverable from IMF IFS</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>- CD legacy: S060; CD2 legacy: S060</t>
+          <t xml:space="preserve">   (the workbook's underlying source) in a future enrichment pass.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>- Book: Shaikh (2016) pp. 523-524 (figure), 875 (Appendix 11.1.II source)</t>
+          <t>4. **Within-chapter unit inconsistency with S1104-A.** S1101 uses X/M;</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>- EPR: `Technical/docs/series/S1101_EPR.md`</t>
+          <t xml:space="preserve">   S1104-A uses (X-M)/(X+M) per Shaikh's authorial choice in Fig 11.7.</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21953,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
@@ -21955,262 +21963,266 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Tolerance: ±0.5% per cell (book-truth pass-through). Expected MAE: 0.0%</t>
+          <t>- CD legacy: S060; CD2 legacy: S060</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>- Book: Shaikh (2016) pp. 523-524 (figure), 875 (Appendix 11.1.II source)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>- EPR: `Technical/docs/series/S1101_EPR.md`</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Tolerance: ±0.5% per cell (book-truth pass-through). Expected MAE: 0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>(direct workbook read). Achieved: MAE 0.0, max 0.0%, n=766. PASS.</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="4">
+    <row r="88">
+      <c r="A88" s="4">
         <f>== EPR: S1101_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t># S1101 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>**Phase**: 6 (Extension)</t>
         </is>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>**Construction**: `composite`</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>**Extension method**: IMF DOTS (Direction of Trade Statistics) per-country X and M continuation; X/M recomputed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>**Status v1**: `not_attempted_v1` (deferred to Phase 9 enrichment)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>## 1. Why this series is extendable</t>
+          <t>**Construction**: `composite`</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>**Extension method**: IMF DOTS (Direction of Trade Statistics) per-country X and M continuation; X/M recomputed.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S1101 components are X and M in current USD published continuously by IMF for</t>
+          <t>**Status v1**: `not_attempted_v1` (deferred to Phase 9 enrichment)</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>all 15 countries (IFS and DOTS are both active). The X/M ratio is the</t>
-        </is>
-      </c>
+      <c r="A95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>canonical published Shaikh figure; the same ratio recomputed from DOTS X and</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>M for post-2009 years is a direct continuation of the same observed series.</t>
-        </is>
-      </c>
+      <c r="A97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>## 1. Why this series is extendable</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>## 2. Classification</t>
-        </is>
-      </c>
+      <c r="A99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>S1101 components are X and M in current USD published continuously by IMF for</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>`composite`. The book series is a per-country pass-through of IMF IFS X and M;</t>
+          <t>all 15 countries (IFS and DOTS are both active). The X/M ratio is the</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>extension fetches the same source for new years and computes X/M identically.</t>
+          <t>canonical published Shaikh figure; the same ratio recomputed from DOTS X and</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>No lazy splice is needed — the X/M ratio is itself reconstructable from raw</t>
+          <t>M for post-2009 years is a direct continuation of the same observed series.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>flows year by year.</t>
-        </is>
-      </c>
+      <c r="A104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>## 2. Classification</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>## 3. Method (planned, v1 = not attempted)</t>
-        </is>
-      </c>
+      <c r="A106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>`composite`. The book series is a per-country pass-through of IMF IFS X and M;</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>extension fetches the same source for new years and computes X/M identically.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>For each country c in {US, UK, DE, JP, ...}:</t>
+          <t>No lazy splice is needed — the X/M ratio is itself reconstructable from raw</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Fetch DOTS_X[c, year] and DOTS_M[c, year] for year in [2010, current]</t>
+          <t>flows year by year.</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    S1101[c, year] = DOTS_X[c, year] / DOTS_M[c, year]</t>
-        </is>
-      </c>
+      <c r="A111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Belgium 1960-1992: preserve AMECO X+M backfill; X/M remains NaN.</t>
+          <t>## 3. Method (planned, v1 = not attempted)</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>```</t>
         </is>
       </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>## 4. No-Proxy disclosure</t>
+          <t>For each country c in {US, UK, DE, JP, ...}:</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Fetch DOTS_X[c, year] and DOTS_M[c, year] for year in [2010, current]</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>None. IMF DOTS publishes the same X and M flows IFS does for the same</t>
+          <t xml:space="preserve">    S1101[c, year] = DOTS_X[c, year] / DOTS_M[c, year]</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>countries; same agency, same concept.</t>
+          <t>Belgium 1960-1992: preserve AMECO X+M backfill; X/M remains NaN.</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>## 5. No-Synthetic disclosure</t>
-        </is>
-      </c>
+      <c r="A120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>## 4. No-Proxy disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>None. NaN propagates if DOTS lacks a country/year.</t>
-        </is>
-      </c>
+      <c r="A122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>None. IMF DOTS publishes the same X and M flows IFS does for the same</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>## 6. Failure-mode table</t>
+          <t>countries; same agency, same concept.</t>
         </is>
       </c>
     </row>
@@ -22220,35 +22232,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>| Failure | Action |</t>
+          <t>## 5. No-Synthetic disclosure</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>| IMF DOTS API down | Loader returns `extension_status: api_unavailable` |</t>
+          <t>None. NaN propagates if DOTS lacks a country/year.</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>| China data missing | S1101-E remains `cd2_addition` placeholder |</t>
-        </is>
-      </c>
+      <c r="A129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>| Belgium pre-1993 X/M | NaN preserved, never imputed |</t>
+          <t>## 6. Failure-mode table</t>
         </is>
       </c>
     </row>
@@ -22258,29 +22262,67 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>## 7. CD2 divergence pre-disclosure</t>
+          <t>| Failure | Action |</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>|---|---|</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CD2 S060 included China (S060-E); RSCD honors this with the `cd2_addition`</t>
+          <t>| IMF DOTS API down | Loader returns `extension_status: api_unavailable` |</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>flag but does not emit S1101-E rows in v1. Other 15-country values match</t>
+          <t>| China data missing | S1101-E remains `cd2_addition` placeholder |</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
+        <is>
+          <t>| Belgium pre-1993 X/M | NaN preserved, never imputed |</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>## 7. CD2 divergence pre-disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>CD2 S060 included China (S060-E); RSCD honors this with the `cd2_addition`</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>flag but does not emit S1101-E rows in v1. Other 15-country values match</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>verbatim.</t>
         </is>
@@ -22783,7 +22825,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -22892,7 +22934,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-18T23:11:01.974196+00:00</t>
+          <t>2026-07-02T06:18:35.194828+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1101_extenbook.xlsx
+++ b/extenbooks/S1101_extenbook.xlsx
@@ -22934,7 +22934,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02T06:18:35.194828+00:00</t>
+          <t>2026-07-11T03:44:22.446612+00:00</t>
         </is>
       </c>
     </row>
@@ -22949,11 +22949,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22976,6 +22976,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IMF_IFS_XM_APPENDIX_11_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful reconstruction of Figure 11.2 (export/import ratios for 15 major OECD countries plus partial Belgium) from IMF IFS; uniform units, no mixing. Country labels assigned (lettered subseries map to US/UK/Germany/Japan).", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1101_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1101_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fig 11.2; 15-country OECD trade balances. China (S1101-E) preserved as cd2_addition flag; not loaded v1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cross_sectional</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ratio_exports_over_imports</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
